--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_12/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_12/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999931091061</v>
+        <v>99.99999997475868</v>
       </c>
       <c r="B2" t="n">
-        <v>92.80583784661205</v>
+        <v>161.2050427865952</v>
       </c>
       <c r="C2" t="n">
-        <v>47.49343194810722</v>
+        <v>40.95731979326771</v>
       </c>
       <c r="D2" t="n">
-        <v>7.135021276627856</v>
+        <v>8.506419697280833</v>
       </c>
       <c r="E2" t="n">
-        <v>3.078819093066243</v>
+        <v>3.210497035248755</v>
       </c>
       <c r="F2" t="n">
-        <v>13.18630908434341</v>
+        <v>13.50555319660893</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02375207070432396</v>
+        <v>0.02340478277570433</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8637381189364527</v>
+        <v>-0.8445973165504386</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9224816962576222</v>
+        <v>-0.9121428912306395</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9541100211351713</v>
+        <v>-0.9454558260493767</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0003264955180469043</v>
+        <v>-0.0001594148680759375</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069678464903</v>
+        <v>-0.5874999998201555</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03138889816538541</v>
+        <v>-0.01061035451889764</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999931091061</v>
+        <v>99.99999997475868</v>
       </c>
       <c r="B3" t="n">
-        <v>92.90886617966513</v>
+        <v>152.3327165830839</v>
       </c>
       <c r="C3" t="n">
-        <v>47.49343194810722</v>
+        <v>40.95731979326771</v>
       </c>
       <c r="D3" t="n">
-        <v>7.135021276627856</v>
+        <v>8.506419697280833</v>
       </c>
       <c r="E3" t="n">
-        <v>3.078819093066243</v>
+        <v>3.210497035248755</v>
       </c>
       <c r="F3" t="n">
-        <v>13.18630908434341</v>
+        <v>13.50555319660893</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02375207070432396</v>
+        <v>0.02340478277570433</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8637381189364527</v>
+        <v>-0.8445973165504386</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9224816962576222</v>
+        <v>-0.9121428912306395</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9541100211351713</v>
+        <v>-0.9454558260493767</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0003264955180469043</v>
+        <v>-0.0001594148680759375</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069678464903</v>
+        <v>-0.5874999998201555</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03138889816538541</v>
+        <v>-0.01061035451889764</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50.23680961639727</v>
+        <v>52.54924801142197</v>
       </c>
       <c r="B4" t="n">
-        <v>96.45682370281686</v>
+        <v>63.90138737133831</v>
       </c>
       <c r="C4" t="n">
-        <v>47.51991893794252</v>
+        <v>40.91108781728804</v>
       </c>
       <c r="D4" t="n">
-        <v>7.982316828459679</v>
+        <v>8.214539252137214</v>
       </c>
       <c r="E4" t="n">
-        <v>3.320384491223975</v>
+        <v>3.192062454640019</v>
       </c>
       <c r="F4" t="n">
-        <v>5.605060828850484</v>
+        <v>6.00115923478459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2757334625624173</v>
+        <v>0.2276951490223749</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.197328497221637e-05</v>
+        <v>-0.001052684534744121</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5688000463507006</v>
+        <v>-0.5695650302909228</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3566377328110104</v>
+        <v>-0.358978541816616</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0007674669023070411</v>
+        <v>-0.000147077710456836</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.583575529639312</v>
+        <v>-0.6003283200761464</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03085156968371766</v>
+        <v>-0.0004393198033697532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>50.23680961639727</v>
+        <v>53.89298851401922</v>
       </c>
       <c r="B5" t="n">
-        <v>96.61931053911933</v>
+        <v>62.01962976287325</v>
       </c>
       <c r="C5" t="n">
-        <v>47.51991893794252</v>
+        <v>47.32407004711408</v>
       </c>
       <c r="D5" t="n">
-        <v>7.982316828459679</v>
+        <v>7.534111677468199</v>
       </c>
       <c r="E5" t="n">
-        <v>3.320384491223975</v>
+        <v>4.694297495294627</v>
       </c>
       <c r="F5" t="n">
-        <v>5.605060828850484</v>
+        <v>6.166757735391897</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2757334625624173</v>
+        <v>0.206778632070025</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.197328497221637e-05</v>
+        <v>-0.07301704945911144</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5688000463507006</v>
+        <v>-0.5943008523644022</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3566377328110104</v>
+        <v>-0.4196432580862724</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0007674669023070411</v>
+        <v>-0.02473784803640182</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.583575529639312</v>
+        <v>-0.5605973416179694</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03085156968371766</v>
+        <v>-0.4053488993586835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67.6562834555402</v>
+        <v>82.93721823196141</v>
       </c>
       <c r="B6" t="n">
-        <v>103.317630312237</v>
+        <v>71.27755296515696</v>
       </c>
       <c r="C6" t="n">
-        <v>47.49618606882274</v>
+        <v>45.52288144154851</v>
       </c>
       <c r="D6" t="n">
-        <v>11.9416814310592</v>
+        <v>10.82770619794496</v>
       </c>
       <c r="E6" t="n">
-        <v>2.61805252511932</v>
+        <v>3.40108207538333</v>
       </c>
       <c r="F6" t="n">
-        <v>7.849931564282093</v>
+        <v>10.32172643725278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09641462914516255</v>
+        <v>0.04497030693107219</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5775829016780807</v>
+        <v>-0.7358788401524239</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7847660402398884</v>
+        <v>-0.8574419127778851</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7944298201318108</v>
+        <v>-0.8901346348624621</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07737375312106452</v>
+        <v>-0.1758493113842755</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3803971550814957</v>
+        <v>-0.4060538766150061</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03135141439277492</v>
+        <v>-0.005084764788556989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>70.37180108620367</v>
+        <v>62.42853446339296</v>
       </c>
       <c r="B7" t="n">
-        <v>146.39807704137</v>
+        <v>172.1880265211859</v>
       </c>
       <c r="C7" t="n">
-        <v>47.67217499126218</v>
+        <v>45.51427141565487</v>
       </c>
       <c r="D7" t="n">
-        <v>11.16950550435241</v>
+        <v>13.14941623688427</v>
       </c>
       <c r="E7" t="n">
-        <v>3.322147017400405</v>
+        <v>4.591537398624803</v>
       </c>
       <c r="F7" t="n">
-        <v>8.12749718310201</v>
+        <v>7.284611659638843</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08305710181752023</v>
+        <v>0.1280644086300525</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6238819719099609</v>
+        <v>-0.3868420886575989</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8050689061673556</v>
+        <v>-0.7064379129890175</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8238267342725507</v>
+        <v>-0.6630997165657774</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.003686366719175707</v>
+        <v>-0.08335810869795725</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4006822611354343</v>
+        <v>-0.3198033080516748</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0248827765925909</v>
+        <v>-0.003171425701081754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95.11392537533527</v>
+        <v>94.56133474955455</v>
       </c>
       <c r="B8" t="n">
-        <v>95.01899057993252</v>
+        <v>154.2611982022323</v>
       </c>
       <c r="C8" t="n">
-        <v>47.82120510465004</v>
+        <v>45.51030636206383</v>
       </c>
       <c r="D8" t="n">
-        <v>7.992454115838002</v>
+        <v>9.093242715641939</v>
       </c>
       <c r="E8" t="n">
-        <v>3.040526546868769</v>
+        <v>3.231002944752275</v>
       </c>
       <c r="F8" t="n">
-        <v>12.25651203431612</v>
+        <v>12.39662735172692</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02820756782002921</v>
+        <v>0.02833165094540473</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8428287481986396</v>
+        <v>-0.8176244063505851</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9112481669980513</v>
+        <v>-0.8977690635041938</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9445748499676412</v>
+        <v>-0.9325928076781077</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.01967139569334674</v>
+        <v>-0.04927789202951839</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5855076548420984</v>
+        <v>-0.5487495100905762</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02133363944109178</v>
+        <v>-0.002290302680850315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60.69260395316402</v>
+        <v>63.89950965620302</v>
       </c>
       <c r="B9" t="n">
-        <v>147.2662071503302</v>
+        <v>152.4040231254447</v>
       </c>
       <c r="C9" t="n">
-        <v>47.79651371960507</v>
+        <v>40.93404617477851</v>
       </c>
       <c r="D9" t="n">
-        <v>12.19392624637159</v>
+        <v>13.53579443855056</v>
       </c>
       <c r="E9" t="n">
-        <v>2.699795493597718</v>
+        <v>3.35771179078518</v>
       </c>
       <c r="F9" t="n">
-        <v>6.864846863632899</v>
+        <v>7.553015056936059</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1446581079143062</v>
+        <v>0.1175971760039873</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4187894871198031</v>
+        <v>-0.4272444723950915</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7193140890498106</v>
+        <v>-0.7223178504822001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6859184524849284</v>
+        <v>-0.6922392817061994</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.004399921882701168</v>
+        <v>-0.06083326863375258</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3283779836217893</v>
+        <v>-0.3302840063004466</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.02228356644210866</v>
+        <v>-0.005490158451271765</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>64.54656646609249</v>
+        <v>59.14777365462836</v>
       </c>
       <c r="B10" t="n">
-        <v>155.2324234526268</v>
+        <v>63.33703106195232</v>
       </c>
       <c r="C10" t="n">
-        <v>47.52721776156093</v>
+        <v>45.61907413528898</v>
       </c>
       <c r="D10" t="n">
-        <v>11.92297666331033</v>
+        <v>7.234420800340793</v>
       </c>
       <c r="E10" t="n">
-        <v>2.97669975608073</v>
+        <v>3.469251939891719</v>
       </c>
       <c r="F10" t="n">
-        <v>7.366872038672343</v>
+        <v>6.980490852849182</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1147386936886253</v>
+        <v>0.1457257211649396</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5151658520072044</v>
+        <v>-0.2930895312567758</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7584146030398818</v>
+        <v>-0.6729398140472933</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7531617027809833</v>
+        <v>-0.5947723353902031</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0205317987207596</v>
+        <v>-0.00443851437709876</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.357167352329941</v>
+        <v>-0.6246025664793129</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03056334002390865</v>
+        <v>-0.02646091895310662</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61.67154748582782</v>
+        <v>57.98546061283128</v>
       </c>
       <c r="B11" t="n">
-        <v>105.5376815979849</v>
+        <v>62.07070515061365</v>
       </c>
       <c r="C11" t="n">
-        <v>47.48286913572966</v>
+        <v>45.51253190905629</v>
       </c>
       <c r="D11" t="n">
-        <v>11.99528086585274</v>
+        <v>7.422997007636081</v>
       </c>
       <c r="E11" t="n">
-        <v>2.897678470801436</v>
+        <v>4.769155818159258</v>
       </c>
       <c r="F11" t="n">
-        <v>7.018221453427993</v>
+        <v>6.801787165912319</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1358653804702786</v>
+        <v>0.1569841391996085</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4458558152170981</v>
+        <v>-0.2504343474138388</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7301728198414187</v>
+        <v>-0.657098063199015</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.705251395678448</v>
+        <v>-0.5619575306995637</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.008183400467521387</v>
+        <v>-0.005747121647825896</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3465501112422628</v>
+        <v>-0.6172412505479314</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0318051079578812</v>
+        <v>-0.002784868679173852</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>93.37230786113756</v>
+        <v>73.70231998817158</v>
       </c>
       <c r="B12" t="n">
-        <v>91.03124598533854</v>
+        <v>174.835011530414</v>
       </c>
       <c r="C12" t="n">
-        <v>47.49343195324158</v>
+        <v>45.51325319777266</v>
       </c>
       <c r="D12" t="n">
-        <v>8.247765408890537</v>
+        <v>11.61840843855696</v>
       </c>
       <c r="E12" t="n">
-        <v>2.770549336489911</v>
+        <v>3.763209023540184</v>
       </c>
       <c r="F12" t="n">
-        <v>11.92017871742055</v>
+        <v>8.77902394364836</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03006562426059924</v>
+        <v>0.06887388227739817</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8343069068644779</v>
+        <v>-0.6240059881010021</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9066694031800584</v>
+        <v>-0.8049802453734867</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9405654080363285</v>
+        <v>-0.8241013801196796</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.009366195377793112</v>
+        <v>-0.03393941427026954</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.572497650568156</v>
+        <v>-0.4001290299157225</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03138889809550652</v>
+        <v>-0.002945155060589816</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>86.46967766844418</v>
+        <v>57.23664834163213</v>
       </c>
       <c r="B13" t="n">
-        <v>148.9882700498874</v>
+        <v>151.9971495924929</v>
       </c>
       <c r="C13" t="n">
-        <v>47.4795098369482</v>
+        <v>45.55019686297239</v>
       </c>
       <c r="D13" t="n">
-        <v>9.46910047036649</v>
+        <v>13.28136242199075</v>
       </c>
       <c r="E13" t="n">
-        <v>3.03913675923717</v>
+        <v>3.580666203285502</v>
       </c>
       <c r="F13" t="n">
-        <v>10.73684969839408</v>
+        <v>6.581845556384653</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03940973517441042</v>
+        <v>0.1776244053899993</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7933212676180703</v>
+        <v>-0.2076770312675444</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8852461989887558</v>
+        <v>-0.6388384217119741</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9203567491747157</v>
+        <v>-0.526311067698489</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0562502641483091</v>
+        <v>-0.02899586344746476</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5209345217087449</v>
+        <v>-0.2828111194341288</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.03194435301242173</v>
+        <v>-0.01115485843830935</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>56.13805077390971</v>
+        <v>79.78685575247235</v>
       </c>
       <c r="B14" t="n">
-        <v>99.64478100119042</v>
+        <v>77.83972432239914</v>
       </c>
       <c r="C14" t="n">
-        <v>47.52208965342017</v>
+        <v>45.59450834758256</v>
       </c>
       <c r="D14" t="n">
-        <v>7.117477144914826</v>
+        <v>10.48152545926044</v>
       </c>
       <c r="E14" t="n">
-        <v>3.183898578536775</v>
+        <v>3.584215633227786</v>
       </c>
       <c r="F14" t="n">
-        <v>6.403028265478156</v>
+        <v>9.650249146210509</v>
       </c>
       <c r="G14" t="n">
-        <v>0.180732354687637</v>
+        <v>0.0515040580706155</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2800612306051845</v>
+        <v>-0.7045954854772052</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6682790517996621</v>
+        <v>-0.8426420346691722</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5843144548461859</v>
+        <v>-0.8725801246122061</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0007742045528485443</v>
+        <v>-2.670797550601693e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6227601366969229</v>
+        <v>-0.458441382689954</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.03076584839267471</v>
+        <v>-0.02100185501834745</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91.60981625563275</v>
+        <v>93.16567408366781</v>
       </c>
       <c r="B15" t="n">
-        <v>84.01288685907797</v>
+        <v>52.89909354702594</v>
       </c>
       <c r="C15" t="n">
-        <v>47.49368870474552</v>
+        <v>45.51939469632074</v>
       </c>
       <c r="D15" t="n">
-        <v>8.488767564385705</v>
+        <v>8.790599965253978</v>
       </c>
       <c r="E15" t="n">
-        <v>3.091277424402139</v>
+        <v>3.980659135547631</v>
       </c>
       <c r="F15" t="n">
-        <v>11.58930144864955</v>
+        <v>12.02634147536472</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03212363990362696</v>
+        <v>0.02977265481199401</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8250125136102192</v>
+        <v>-0.8111351364929367</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9017289613498627</v>
+        <v>-0.8949529811059289</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9361144707291033</v>
+        <v>-0.929527219841271</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.003918075854991538</v>
+        <v>-0.01682412631653982</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5593317153766005</v>
+        <v>-0.06633820535624817</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.03138540368985585</v>
+        <v>-0.004309932515719206</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>76.676796538408</v>
+        <v>63.48190407724472</v>
       </c>
       <c r="B16" t="n">
-        <v>90.2506467394325</v>
+        <v>146.7953679304411</v>
       </c>
       <c r="C16" t="n">
-        <v>46.51309151428072</v>
+        <v>40.96098523515855</v>
       </c>
       <c r="D16" t="n">
-        <v>10.63371764847673</v>
+        <v>13.18265080833766</v>
       </c>
       <c r="E16" t="n">
-        <v>2.92876353425543</v>
+        <v>3.506247003242985</v>
       </c>
       <c r="F16" t="n">
-        <v>9.09903308935559</v>
+        <v>7.420548627561763</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06066766077409401</v>
+        <v>0.1202399771877122</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.707198519130541</v>
+        <v>-0.4164005308445867</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8430913127497354</v>
+        <v>-0.7180836848468368</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8736276345213689</v>
+        <v>-0.6845168429771752</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01562811460422575</v>
+        <v>-0.003981578140004548</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4477810168103575</v>
+        <v>-0.3273085665503687</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.04548059557698352</v>
+        <v>-0.01141675173488121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81.17895568585007</v>
+        <v>92.28545886227346</v>
       </c>
       <c r="B17" t="n">
-        <v>119.0858553931465</v>
+        <v>52.89909354702594</v>
       </c>
       <c r="C17" t="n">
-        <v>47.87441303607284</v>
+        <v>45.51939469632074</v>
       </c>
       <c r="D17" t="n">
-        <v>10.11375374276128</v>
+        <v>8.662485590653789</v>
       </c>
       <c r="E17" t="n">
-        <v>2.598921114557299</v>
+        <v>3.633792861739873</v>
       </c>
       <c r="F17" t="n">
-        <v>9.831021894465922</v>
+        <v>11.80778992181742</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04936301427393246</v>
+        <v>0.03074009788831891</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7519244926682294</v>
+        <v>-0.8059448398052651</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8645628809664205</v>
+        <v>-0.8922814339230294</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.898561609557383</v>
+        <v>-0.926955875987482</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.05156376928844851</v>
+        <v>-0.0378702256394489</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4814124595770385</v>
+        <v>-0.0009634493014839171</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.01928662382675057</v>
+        <v>-0.004309932515719206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89.88491104323785</v>
+        <v>65.3211093623528</v>
       </c>
       <c r="B18" t="n">
-        <v>86.99681955584494</v>
+        <v>169.3898015802543</v>
       </c>
       <c r="C18" t="n">
-        <v>44.63079258927112</v>
+        <v>40.96098523515855</v>
       </c>
       <c r="D18" t="n">
-        <v>9.175142188767383</v>
+        <v>13.0836333596609</v>
       </c>
       <c r="E18" t="n">
-        <v>3.060694410341196</v>
+        <v>3.349451727508775</v>
       </c>
       <c r="F18" t="n">
-        <v>11.36653320612553</v>
+        <v>7.679557721442841</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03439301293881324</v>
+        <v>0.1080649623013112</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.815113782435806</v>
+        <v>-0.4634908313512017</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8964921237223715</v>
+        <v>-0.73694890772712</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9312805796354542</v>
+        <v>-0.7178859209187143</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.03844779629698666</v>
+        <v>-0.0185327227109626</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5464465531624733</v>
+        <v>-0.3404129042067636</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.07905116639188189</v>
+        <v>-0.01141675173488121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54.21152423461568</v>
+        <v>75.72342624206944</v>
       </c>
       <c r="B19" t="n">
-        <v>85.53907795419997</v>
+        <v>151.9964784569409</v>
       </c>
       <c r="C19" t="n">
-        <v>47.84871913624379</v>
+        <v>45.51670064151129</v>
       </c>
       <c r="D19" t="n">
-        <v>7.409635673319732</v>
+        <v>11.62259225540613</v>
       </c>
       <c r="E19" t="n">
-        <v>2.684675478707589</v>
+        <v>3.580350359331538</v>
       </c>
       <c r="F19" t="n">
-        <v>6.138014967803247</v>
+        <v>9.135852760666754</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2063020637201808</v>
+        <v>0.06246142121712456</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2018142076765768</v>
+        <v>-0.6525234433787921</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6395532745923679</v>
+        <v>-0.8177263766955386</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5232091884919229</v>
+        <v>-0.8415745946900958</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.007250965860532741</v>
+        <v>-0.07183215847932256</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6099678810657163</v>
+        <v>-0.4145294119747447</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.02027511957798487</v>
+        <v>-0.00371125366917649</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>83.76872018469918</v>
+        <v>95.68488986189934</v>
       </c>
       <c r="B20" t="n">
-        <v>94.58175125397936</v>
+        <v>154.2611982022323</v>
       </c>
       <c r="C20" t="n">
-        <v>47.66455479226735</v>
+        <v>45.51030636206383</v>
       </c>
       <c r="D20" t="n">
-        <v>9.682554015177329</v>
+        <v>9.093242715641939</v>
       </c>
       <c r="E20" t="n">
-        <v>3.040524816331443</v>
+        <v>3.231002944752275</v>
       </c>
       <c r="F20" t="n">
-        <v>10.2380002138354</v>
+        <v>12.64844813339015</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04408348305810765</v>
+        <v>0.02721669132028378</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7735252569487651</v>
+        <v>-0.8236767744045678</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8752629900076195</v>
+        <v>-0.9009439188717009</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9101013736866513</v>
+        <v>-0.9355352313341642</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02937754238007047</v>
+        <v>-0.08291609104809666</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5007581809675654</v>
+        <v>-0.5567548402660327</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.02513991733153575</v>
+        <v>-0.002290302680850315</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>51.04055719027194</v>
+        <v>61.80032794320527</v>
       </c>
       <c r="B21" t="n">
-        <v>95.61269624232906</v>
+        <v>152.0453534309488</v>
       </c>
       <c r="C21" t="n">
-        <v>46.26989331945647</v>
+        <v>45.55444517911759</v>
       </c>
       <c r="D21" t="n">
-        <v>7.992454115838002</v>
+        <v>12.71193151175911</v>
       </c>
       <c r="E21" t="n">
-        <v>3.038911735477038</v>
+        <v>3.595893160838248</v>
       </c>
       <c r="F21" t="n">
-        <v>5.735199870757346</v>
+        <v>7.105366317501633</v>
       </c>
       <c r="G21" t="n">
-        <v>0.259654345684926</v>
+        <v>0.1326211810462033</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.04588010318569589</v>
+        <v>-0.3687352699485633</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5844704900897129</v>
+        <v>-0.6994833286864246</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3955143612965731</v>
+        <v>-0.6498773255751999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005001592693961342</v>
+        <v>-0.01055720215197898</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5889124633478581</v>
+        <v>-0.3153273365953375</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.04295383856330263</v>
+        <v>-0.01209892869279652</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51.63165397684119</v>
+        <v>87.30193010534411</v>
       </c>
       <c r="B22" t="n">
-        <v>91.56867922229874</v>
+        <v>68.49115454979287</v>
       </c>
       <c r="C22" t="n">
-        <v>47.83694965106997</v>
+        <v>45.60109452781442</v>
       </c>
       <c r="D22" t="n">
-        <v>7.786814827585443</v>
+        <v>9.608872236479138</v>
       </c>
       <c r="E22" t="n">
-        <v>3.316064942468653</v>
+        <v>3.506469221028604</v>
       </c>
       <c r="F22" t="n">
-        <v>5.791017101217416</v>
+        <v>10.95080568221627</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2483641881465196</v>
+        <v>0.03737416581306165</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.07796055600845095</v>
+        <v>-0.772335253799443</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5956014103052246</v>
+        <v>-0.8752808973058083</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4224084522584268</v>
+        <v>-0.9097603533393152</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.007423545710046781</v>
+        <v>-0.01726705691808277</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5928373826481388</v>
+        <v>-0.3139185066632485</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.02072791522854522</v>
+        <v>-0.02246545062542543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55.06870221287912</v>
+        <v>68.71515237226357</v>
       </c>
       <c r="B23" t="n">
-        <v>85.53907795419997</v>
+        <v>154.2453328365424</v>
       </c>
       <c r="C23" t="n">
-        <v>47.52021413375224</v>
+        <v>45.55493648025706</v>
       </c>
       <c r="D23" t="n">
-        <v>7.377881393985056</v>
+        <v>11.99357551032061</v>
       </c>
       <c r="E23" t="n">
-        <v>2.890615509795574</v>
+        <v>3.582330697012616</v>
       </c>
       <c r="F23" t="n">
-        <v>6.272019251364216</v>
+        <v>8.021356347645668</v>
       </c>
       <c r="G23" t="n">
-        <v>0.194449778039773</v>
+        <v>0.08912447785702438</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2379219955887203</v>
+        <v>-0.5382538093883307</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6526983028767668</v>
+        <v>-0.7679485874310046</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5516571845519204</v>
+        <v>-0.7689385517964494</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.02657162710408674</v>
+        <v>-0.008121531344128536</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6156595959711361</v>
+        <v>-0.3645954606523779</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.03083991243698074</v>
+        <v>-0.01220810672379169</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>50.71763905876941</v>
+        <v>82.3867084595896</v>
       </c>
       <c r="B24" t="n">
-        <v>87.74470111500132</v>
+        <v>71.62318713281917</v>
       </c>
       <c r="C24" t="n">
-        <v>47.82183452231745</v>
+        <v>45.5088269690084</v>
       </c>
       <c r="D24" t="n">
-        <v>7.964317165856507</v>
+        <v>9.910744272963694</v>
       </c>
       <c r="E24" t="n">
-        <v>3.038755191724484</v>
+        <v>3.942106201442525</v>
       </c>
       <c r="F24" t="n">
-        <v>5.681874936265355</v>
+        <v>10.02603575889581</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2659614284702213</v>
+        <v>0.04584395467278107</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0278261878758931</v>
+        <v>-0.730873712125182</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5782707313571743</v>
+        <v>-0.8550875783699441</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.380264730955621</v>
+        <v>-0.8873824227741695</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.01919102974828284</v>
+        <v>-0.001704213925451717</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5867682669395149</v>
+        <v>-0.4299093000844504</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.02130942448368489</v>
+        <v>-0.001961548668532875</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>63.43903628171719</v>
+        <v>90.68028777800023</v>
       </c>
       <c r="B25" t="n">
-        <v>171.4214510306455</v>
+        <v>52.66802177959322</v>
       </c>
       <c r="C25" t="n">
-        <v>47.53863107474334</v>
+        <v>45.51939469632074</v>
       </c>
       <c r="D25" t="n">
-        <v>11.9416814310592</v>
+        <v>8.790599965253978</v>
       </c>
       <c r="E25" t="n">
-        <v>2.81186199178055</v>
+        <v>3.972349150664269</v>
       </c>
       <c r="F25" t="n">
-        <v>7.205618288218386</v>
+        <v>11.48803557936974</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1223816347148827</v>
+        <v>0.03266360638596137</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4898928329000052</v>
+        <v>-0.7959313386832811</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7479921966968547</v>
+        <v>-0.8871598175874779</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7359294233738901</v>
+        <v>-0.9219290971410424</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.004455466044473801</v>
+        <v>-0.01155698361529115</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3488940246246438</v>
+        <v>-0.07052086295332291</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.03011262967004247</v>
+        <v>-0.004309932515719206</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>62.8481265162708</v>
+        <v>61.17162957282041</v>
       </c>
       <c r="B26" t="n">
-        <v>152.6943437224167</v>
+        <v>153.4843847964765</v>
       </c>
       <c r="C26" t="n">
-        <v>47.49395809053431</v>
+        <v>45.5538358862179</v>
       </c>
       <c r="D26" t="n">
-        <v>12.01178623449686</v>
+        <v>12.71034250454992</v>
       </c>
       <c r="E26" t="n">
-        <v>3.421720433736315</v>
+        <v>3.606046735860612</v>
       </c>
       <c r="F26" t="n">
-        <v>7.130657955767236</v>
+        <v>7.013924358050407</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1267733517386424</v>
+        <v>0.137788441391912</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4756349542901922</v>
+        <v>-0.3494327040598297</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7421623994109259</v>
+        <v>-0.6920315209056856</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7260763401135047</v>
+        <v>-0.6355809360987886</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.004874295592242526</v>
+        <v>-0.000632678254265152</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3444798874726567</v>
+        <v>-0.3108478607063454</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.03138173733071798</v>
+        <v>-0.01196353027064528</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>53.29675749080756</v>
+        <v>98.29706037639826</v>
       </c>
       <c r="B27" t="n">
-        <v>96.64917642218568</v>
+        <v>175.7347932083387</v>
       </c>
       <c r="C27" t="n">
-        <v>47.50073899020043</v>
+        <v>45.56839785677359</v>
       </c>
       <c r="D27" t="n">
-        <v>7.613253414871497</v>
+        <v>8.346291733635871</v>
       </c>
       <c r="E27" t="n">
-        <v>2.724230200469415</v>
+        <v>4.888312530570402</v>
       </c>
       <c r="F27" t="n">
-        <v>6.021198859444632</v>
+        <v>13.09461538166836</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2201142050674531</v>
+        <v>0.02478809592797927</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1605936392777338</v>
+        <v>-0.8368276035856683</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6247254670706783</v>
+        <v>-0.9079718296558702</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4901945289822974</v>
+        <v>-0.941823693761987</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.01785978226054572</v>
+        <v>-0.005774791390275888</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.6038937731876034</v>
+        <v>-0.5753665551818377</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.03128944881927212</v>
+        <v>-0.01519952372746602</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52.49222874160867</v>
+        <v>71.67387534894402</v>
       </c>
       <c r="B28" t="n">
-        <v>94.97973983481984</v>
+        <v>170.0367806145419</v>
       </c>
       <c r="C28" t="n">
-        <v>47.82183452231745</v>
+        <v>45.55573001311416</v>
       </c>
       <c r="D28" t="n">
-        <v>7.992454115838002</v>
+        <v>11.76243407806093</v>
       </c>
       <c r="E28" t="n">
-        <v>3.040526546868769</v>
+        <v>3.344801160005399</v>
       </c>
       <c r="F28" t="n">
-        <v>5.97336652775898</v>
+        <v>8.463363894386719</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2335458925083055</v>
+        <v>0.07628854147041689</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1217071379432293</v>
+        <v>-0.5919856742861787</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6108777056004909</v>
+        <v>-0.7909268386131482</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4585127737761223</v>
+        <v>-0.8039438992341121</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.08703001663394146</v>
+        <v>-0.02191187316454074</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5985516524264856</v>
+        <v>-0.3856763618612262</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02130942448368489</v>
+        <v>-0.0123844473587037</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>83.44582155080289</v>
+        <v>55.79624503697107</v>
       </c>
       <c r="B29" t="n">
-        <v>115.0232185368303</v>
+        <v>84.76097762918069</v>
       </c>
       <c r="C29" t="n">
-        <v>47.49260791103072</v>
+        <v>45.5134892527695</v>
       </c>
       <c r="D29" t="n">
-        <v>9.682554015177329</v>
+        <v>7.779100677105371</v>
       </c>
       <c r="E29" t="n">
-        <v>3.052598423981863</v>
+        <v>3.890107163292995</v>
       </c>
       <c r="F29" t="n">
-        <v>10.1744115940415</v>
+        <v>6.483479116609852</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0446881603766654</v>
+        <v>0.1814953610158524</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.770990802800091</v>
+        <v>-0.1601063354618229</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8740012726853013</v>
+        <v>-0.6243228999259747</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.908766587922523</v>
+        <v>-0.4904255510467743</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01730403577241276</v>
+        <v>-0.0150604912352776</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.4983461056566577</v>
+        <v>-0.6033762185674834</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.03141862518649739</v>
+        <v>-0.002997611726555938</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>65.77896536062374</v>
+        <v>59.62323775140383</v>
       </c>
       <c r="B30" t="n">
-        <v>102.45124689329</v>
+        <v>173.7468340746909</v>
       </c>
       <c r="C30" t="n">
-        <v>47.52205866333214</v>
+        <v>45.52871083991698</v>
       </c>
       <c r="D30" t="n">
-        <v>11.93488528679504</v>
+        <v>12.90508793602981</v>
       </c>
       <c r="E30" t="n">
-        <v>2.54130896539627</v>
+        <v>4.616432144028845</v>
       </c>
       <c r="F30" t="n">
-        <v>7.556921793785004</v>
+        <v>6.832037881464203</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1069760602328721</v>
+        <v>0.1518831861672214</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5413068638287839</v>
+        <v>-0.2981394073752353</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7693373845377295</v>
+        <v>-0.6724644611534712</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7706726470855594</v>
+        <v>-0.5968794660719678</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.04395508982763555</v>
+        <v>-0.006852984952836608</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.3663734580071909</v>
+        <v>-0.2998155689787523</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.03076707218749359</v>
+        <v>-0.006380186648217157</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>55.73161007998387</v>
+        <v>80.1883149763419</v>
       </c>
       <c r="B31" t="n">
-        <v>76.26823348859631</v>
+        <v>165.810968689764</v>
       </c>
       <c r="C31" t="n">
-        <v>45.49391013140816</v>
+        <v>45.8718014771756</v>
       </c>
       <c r="D31" t="n">
-        <v>7.343199616834008</v>
+        <v>11.39306199099877</v>
       </c>
       <c r="E31" t="n">
-        <v>3.032645980424619</v>
+        <v>3.952092642472704</v>
       </c>
       <c r="F31" t="n">
-        <v>6.38319644462777</v>
+        <v>9.927151934106096</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1859112869653586</v>
+        <v>0.05083494564118236</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2643247070384817</v>
+        <v>-0.7059004485422961</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6624128105086178</v>
+        <v>-0.8423193484614102</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5721750905757954</v>
+        <v>-0.8730100167603912</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.002090401334483343</v>
+        <v>-0.126219917026331</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.6200613452971793</v>
+        <v>-0.446341744206436</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.05191750997353872</v>
+        <v>-0.0826225504834667</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>57.08841831780855</v>
+        <v>71.3257599395981</v>
       </c>
       <c r="B32" t="n">
-        <v>74.28945911007744</v>
+        <v>169.8106562372915</v>
       </c>
       <c r="C32" t="n">
-        <v>46.23960295507403</v>
+        <v>45.55573001311416</v>
       </c>
       <c r="D32" t="n">
-        <v>7.270366384754795</v>
+        <v>11.74045370746958</v>
       </c>
       <c r="E32" t="n">
-        <v>2.661222897221098</v>
+        <v>3.344801160005399</v>
       </c>
       <c r="F32" t="n">
-        <v>6.602728758624695</v>
+        <v>8.400211776656995</v>
       </c>
       <c r="G32" t="n">
-        <v>0.169856135945821</v>
+        <v>0.0776444402049402</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3146679060294918</v>
+        <v>-0.5861495466077755</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6812087909004259</v>
+        <v>-0.788403279955987</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6106273986413464</v>
+        <v>-0.8002153686718219</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.05660806281035302</v>
+        <v>-0.01199105559047093</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.6290706360942527</v>
+        <v>-0.3831960395696364</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.04343003831708404</v>
+        <v>-0.0123844473587037</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>53.441500372865</v>
+        <v>96.88054436437693</v>
       </c>
       <c r="B33" t="n">
-        <v>96.64917642218568</v>
+        <v>69.51864934921831</v>
       </c>
       <c r="C33" t="n">
-        <v>47.50073899020043</v>
+        <v>45.53181571998104</v>
       </c>
       <c r="D33" t="n">
-        <v>7.762920482604107</v>
+        <v>9.207473591931743</v>
       </c>
       <c r="E33" t="n">
-        <v>3.343335856521875</v>
+        <v>4.083877613934744</v>
       </c>
       <c r="F33" t="n">
-        <v>6.076586198741479</v>
+        <v>12.94398055998253</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2180246323667329</v>
+        <v>0.02610575448946949</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1671620507837585</v>
+        <v>-0.8297964090395449</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6270479318426012</v>
+        <v>-0.9041692861871766</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4954687109793028</v>
+        <v>-0.9384753651992045</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.06061451483184905</v>
+        <v>-0.1408088969408301</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.6048548748959426</v>
+        <v>-0.5652738785961856</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.03128944881927212</v>
+        <v>-0.007070159995787584</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>97.55655289068343</v>
+        <v>66.83216922553595</v>
       </c>
       <c r="B34" t="n">
-        <v>108.4319012850849</v>
+        <v>146.3462993262808</v>
       </c>
       <c r="C34" t="n">
-        <v>47.82120510465004</v>
+        <v>40.96098523515855</v>
       </c>
       <c r="D34" t="n">
-        <v>7.82090525489816</v>
+        <v>13.18265080833766</v>
       </c>
       <c r="E34" t="n">
-        <v>2.633292807495973</v>
+        <v>3.339667066409317</v>
       </c>
       <c r="F34" t="n">
-        <v>12.77088961888737</v>
+        <v>7.934890213860418</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02587153302865305</v>
+        <v>0.09935402656289177</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8537661527646141</v>
+        <v>-0.4982671075548517</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9171709939645305</v>
+        <v>-0.7511263759749176</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.949615486192293</v>
+        <v>-0.7419001490701342</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0748331759855512</v>
+        <v>-0.05717805852999571</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.6037542527060202</v>
+        <v>-0.3511792057319436</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.02133363944109178</v>
+        <v>-0.01141675173488121</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>51.97477034178335</v>
+        <v>78.36049102549076</v>
       </c>
       <c r="B35" t="n">
-        <v>91.47457520454098</v>
+        <v>77.19807084789828</v>
       </c>
       <c r="C35" t="n">
-        <v>47.4967985820923</v>
+        <v>45.53149042211687</v>
       </c>
       <c r="D35" t="n">
-        <v>7.82090525489816</v>
+        <v>10.57256143895776</v>
       </c>
       <c r="E35" t="n">
-        <v>2.633292807495973</v>
+        <v>4.84764088958364</v>
       </c>
       <c r="F35" t="n">
-        <v>5.847486065742499</v>
+        <v>9.400179080388806</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2422247024073046</v>
+        <v>0.05494518097489804</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.09581829666703649</v>
+        <v>-0.6887113600803335</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6018251863525158</v>
+        <v>-0.8352593485493212</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4372290302297317</v>
+        <v>-0.8634217442638132</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.02142701400701208</v>
+        <v>-0.02905297110534129</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5951156965784513</v>
+        <v>-0.4627036826911808</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.03134307804499356</v>
+        <v>-0.006997871581528592</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>80.51407583763873</v>
+        <v>54.41584658503169</v>
       </c>
       <c r="B36" t="n">
-        <v>99.64196242082538</v>
+        <v>63.90138737133831</v>
       </c>
       <c r="C36" t="n">
-        <v>46.47736456947375</v>
+        <v>40.91108781728804</v>
       </c>
       <c r="D36" t="n">
-        <v>10.0832016164307</v>
+        <v>8.217528854639642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.595647658388709</v>
+        <v>3.443921829576982</v>
       </c>
       <c r="F36" t="n">
-        <v>9.687700467632009</v>
+        <v>6.315391256171269</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05080547237954022</v>
+        <v>0.1996621617384618</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7459852008512818</v>
+        <v>-0.09891781778510664</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8616789626152916</v>
+        <v>-0.6032932954393876</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8953345843549385</v>
+        <v>-0.4410671855064805</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.000651933074235996</v>
+        <v>-0.02016845286724002</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.4764457607488676</v>
+        <v>-0.5960394060091625</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.04429065914931734</v>
+        <v>-0.0004393198033697532</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>54.4968492839692</v>
+        <v>88.69294027119038</v>
       </c>
       <c r="B37" t="n">
-        <v>96.18067137466642</v>
+        <v>63.27052599780733</v>
       </c>
       <c r="C37" t="n">
-        <v>47.84609805777509</v>
+        <v>45.51367237308176</v>
       </c>
       <c r="D37" t="n">
-        <v>7.786760731360153</v>
+        <v>9.144599192435308</v>
       </c>
       <c r="E37" t="n">
-        <v>3.101625657296772</v>
+        <v>3.384823811880714</v>
       </c>
       <c r="F37" t="n">
-        <v>6.265459038663455</v>
+        <v>11.14034784116247</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2026116067609299</v>
+        <v>0.03530865205226143</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2137882262472452</v>
+        <v>-0.7824986363575616</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6438367852090912</v>
+        <v>-0.8803676277631953</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.532643051091835</v>
+        <v>-0.9150565909012738</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1112162701179553</v>
+        <v>-0.02444250894074578</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6118624570784891</v>
+        <v>-0.156639254915084</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.02037595771260863</v>
+        <v>-0.003038305129279412</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88.44936994372203</v>
+        <v>58.06368334176275</v>
       </c>
       <c r="B38" t="n">
-        <v>83.70252460259162</v>
+        <v>152.0610738539541</v>
       </c>
       <c r="C38" t="n">
-        <v>46.22544539684516</v>
+        <v>45.5552191244805</v>
       </c>
       <c r="D38" t="n">
-        <v>9.107725160078594</v>
+        <v>13.17305504026076</v>
       </c>
       <c r="E38" t="n">
-        <v>3.006556816113542</v>
+        <v>3.580666203285502</v>
       </c>
       <c r="F38" t="n">
-        <v>11.05368136627834</v>
+        <v>6.672283170058428</v>
       </c>
       <c r="G38" t="n">
-        <v>0.036356249521448</v>
+        <v>0.1681358014597146</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8064048854376493</v>
+        <v>-0.2406856165058759</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8919827854858297</v>
+        <v>-0.6509752906218075</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9269670542973408</v>
+        <v>-0.5523843514723833</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.01348558975817169</v>
+        <v>-0.02495885480452023</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5357229610488948</v>
+        <v>-0.2887037438100596</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.04365261159674603</v>
+        <v>-0.01227091655122262</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>58.20776884691364</v>
+        <v>57.05472800396811</v>
       </c>
       <c r="B39" t="n">
-        <v>87.9069258225237</v>
+        <v>63.48750365236905</v>
       </c>
       <c r="C39" t="n">
-        <v>46.20417085374159</v>
+        <v>45.55731412207967</v>
       </c>
       <c r="D39" t="n">
-        <v>6.912115595906851</v>
+        <v>7.701521626932558</v>
       </c>
       <c r="E39" t="n">
-        <v>2.551988812473293</v>
+        <v>3.330015224264834</v>
       </c>
       <c r="F39" t="n">
-        <v>6.727910263851522</v>
+        <v>6.692195036853958</v>
       </c>
       <c r="G39" t="n">
-        <v>0.157761875030151</v>
+        <v>0.1669327965065319</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.3529147835625415</v>
+        <v>-0.2136223303418681</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6957710744234481</v>
+        <v>-0.6435996298725647</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6392498816734095</v>
+        <v>-0.5331164977847065</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.008800645466446825</v>
+        <v>-0.04270523193907445</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.6365031929872845</v>
+        <v>-0.611346610691798</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.04398707215522008</v>
+        <v>-0.01273647157326016</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>66.64381059290687</v>
+        <v>55.1559805351166</v>
       </c>
       <c r="B40" t="n">
-        <v>146.8248888951422</v>
+        <v>63.48750365236905</v>
       </c>
       <c r="C40" t="n">
-        <v>46.33421292765691</v>
+        <v>45.53090091274374</v>
       </c>
       <c r="D40" t="n">
-        <v>11.75538753875005</v>
+        <v>7.65489194419149</v>
       </c>
       <c r="E40" t="n">
-        <v>2.981238722017173</v>
+        <v>3.329517469559428</v>
       </c>
       <c r="F40" t="n">
-        <v>7.650400728837712</v>
+        <v>6.347052177331788</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1018137358026571</v>
+        <v>0.1894156120003188</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5586454811280736</v>
+        <v>-0.1343700871567474</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7767035468714359</v>
+        <v>-0.615799493851047</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7821219794520142</v>
+        <v>-0.4701377218300243</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.005499389696134118</v>
+        <v>-0.01369265054243265</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3728339121979524</v>
+        <v>-0.5667424371516349</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.042670887950387</v>
+        <v>-0.006866869498608763</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>57.44769779605531</v>
+        <v>85.92504326942924</v>
       </c>
       <c r="B41" t="n">
-        <v>74.46347145623325</v>
+        <v>67.32832689019367</v>
       </c>
       <c r="C41" t="n">
-        <v>46.18508639020483</v>
+        <v>45.60109452781442</v>
       </c>
       <c r="D41" t="n">
-        <v>7.135024797856666</v>
+        <v>9.608746711824018</v>
       </c>
       <c r="E41" t="n">
-        <v>2.661222897221098</v>
+        <v>3.638674234009912</v>
       </c>
       <c r="F41" t="n">
-        <v>6.63682062932204</v>
+        <v>10.66978730917353</v>
       </c>
       <c r="G41" t="n">
-        <v>0.165827535895665</v>
+        <v>0.039503167916893</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.3272864909463549</v>
+        <v>-0.7616707921780042</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6859922687424305</v>
+        <v>-0.870015308478873</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6201334627047017</v>
+        <v>-0.9041237023738071</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.03540539340345025</v>
+        <v>-0.03994741242577032</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.6314562740987328</v>
+        <v>-0.2765814583247334</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.04428710211598646</v>
+        <v>-0.02246545062542543</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>98.04796540763279</v>
+        <v>99.69962845503876</v>
       </c>
       <c r="B42" t="n">
-        <v>102.3524940144821</v>
+        <v>67.32832689019367</v>
       </c>
       <c r="C42" t="n">
-        <v>47.49686884939612</v>
+        <v>45.60109452781442</v>
       </c>
       <c r="D42" t="n">
-        <v>7.66462462659708</v>
+        <v>8.504582404131483</v>
       </c>
       <c r="E42" t="n">
-        <v>2.633677357146001</v>
+        <v>3.638674234009912</v>
       </c>
       <c r="F42" t="n">
-        <v>12.84504895768685</v>
+        <v>13.45548756216799</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02542094535156674</v>
+        <v>0.02364920851344277</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.8558572937941497</v>
+        <v>-0.8432483978349772</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.9183007113072746</v>
+        <v>-0.9114086138566214</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9505670704577834</v>
+        <v>-0.9448281072501779</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.05102286727742474</v>
+        <v>-0.09095589196526657</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.6074251384737974</v>
+        <v>-0.5853598527421512</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.03134212170214886</v>
+        <v>-0.02246545062542543</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>71.08329726396626</v>
+        <v>89.68896713567652</v>
       </c>
       <c r="B43" t="n">
-        <v>145.4221097128856</v>
+        <v>63.20629997553311</v>
       </c>
       <c r="C43" t="n">
-        <v>47.499394461517</v>
+        <v>45.51597272392254</v>
       </c>
       <c r="D43" t="n">
-        <v>11.76659050469352</v>
+        <v>8.985093054752825</v>
       </c>
       <c r="E43" t="n">
-        <v>2.97441278061788</v>
+        <v>3.373282503133696</v>
       </c>
       <c r="F43" t="n">
-        <v>8.369517933169808</v>
+        <v>11.31708843000838</v>
       </c>
       <c r="G43" t="n">
-        <v>0.08033978631966086</v>
+        <v>0.03395015842483706</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.6344550087301509</v>
+        <v>-0.7893773395985839</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.8096761121585762</v>
+        <v>-0.8838334741367523</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.8303318105048746</v>
+        <v>-0.9185937498613638</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.1115818025281587</v>
+        <v>-0.02175494243224735</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.4059971871959068</v>
+        <v>-0.1134780907873514</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.03130774794724947</v>
+        <v>-0.003549494205010439</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>72.4751034083383</v>
+        <v>55.26020920355236</v>
       </c>
       <c r="B44" t="n">
-        <v>105.0124243250925</v>
+        <v>62.91791698678182</v>
       </c>
       <c r="C44" t="n">
-        <v>47.49739327158731</v>
+        <v>45.51352600533964</v>
       </c>
       <c r="D44" t="n">
-        <v>11.10475890935767</v>
+        <v>7.698229301870688</v>
       </c>
       <c r="E44" t="n">
-        <v>3.391431196442184</v>
+        <v>3.36468353776137</v>
       </c>
       <c r="F44" t="n">
-        <v>8.4646895965643</v>
+        <v>6.373407185926537</v>
       </c>
       <c r="G44" t="n">
-        <v>0.07456913162831778</v>
+        <v>0.1881124978958937</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.6548620689645559</v>
+        <v>-0.13915874102943</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8189256192747767</v>
+        <v>-0.6174897568589482</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.8428156138133136</v>
+        <v>-0.4740256739336071</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.03089474988405942</v>
+        <v>-0.02834854276141135</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.4163940761449254</v>
+        <v>-0.5626167190260525</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.03133498428001084</v>
+        <v>-0.003005778964365324</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>79.11911666634074</v>
+        <v>85.92504326942924</v>
       </c>
       <c r="B45" t="n">
-        <v>104.9161375550999</v>
+        <v>67.32832689019367</v>
       </c>
       <c r="C45" t="n">
-        <v>47.49566046003687</v>
+        <v>45.60109452781442</v>
       </c>
       <c r="D45" t="n">
-        <v>10.25194425104042</v>
+        <v>9.608746711824018</v>
       </c>
       <c r="E45" t="n">
-        <v>2.854990864416756</v>
+        <v>3.875166255349252</v>
       </c>
       <c r="F45" t="n">
-        <v>9.46415446266638</v>
+        <v>10.66978730917353</v>
       </c>
       <c r="G45" t="n">
-        <v>0.05411360609177528</v>
+        <v>0.039503167916893</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.7327604728979065</v>
+        <v>-0.7616707921780042</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8552749509558807</v>
+        <v>-0.870015308478873</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8880498532379874</v>
+        <v>-0.9041237023738071</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.02079284243539989</v>
+        <v>-0.03994741242577032</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.4660253184688519</v>
+        <v>-0.2765814583247334</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.03135856796454833</v>
+        <v>-0.02246545062542543</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>73.91328963194255</v>
+        <v>65.76050870249479</v>
       </c>
       <c r="B46" t="n">
-        <v>96.60307229580057</v>
+        <v>173.7468340746909</v>
       </c>
       <c r="C46" t="n">
-        <v>47.49390034825772</v>
+        <v>45.87004031895581</v>
       </c>
       <c r="D46" t="n">
-        <v>11.03918502425959</v>
+        <v>12.87432114029869</v>
       </c>
       <c r="E46" t="n">
-        <v>2.930397971021655</v>
+        <v>4.616432144028845</v>
       </c>
       <c r="F46" t="n">
-        <v>8.697017563688446</v>
+        <v>7.752071491720081</v>
       </c>
       <c r="G46" t="n">
-        <v>0.06941017821314471</v>
+        <v>0.1054281262834603</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6740782322302972</v>
+        <v>-0.4739366826613468</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8276761020144081</v>
+        <v>-0.7411826345365833</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8543179050751388</v>
+        <v>-0.725155394254219</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.04872093587955309</v>
+        <v>-0.1007850275100698</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.4271374275198886</v>
+        <v>-0.3435436245052754</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.03138252320707859</v>
+        <v>-0.08223118199017942</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>74.1316943352454</v>
+        <v>54.2444002864173</v>
       </c>
       <c r="B47" t="n">
-        <v>105.6876921230804</v>
+        <v>64.30180326821159</v>
       </c>
       <c r="C47" t="n">
-        <v>46.2853377347235</v>
+        <v>41.26927696622869</v>
       </c>
       <c r="D47" t="n">
-        <v>10.94191811292855</v>
+        <v>8.218013731390402</v>
       </c>
       <c r="E47" t="n">
-        <v>2.683980080924406</v>
+        <v>4.296468477678562</v>
       </c>
       <c r="F47" t="n">
-        <v>8.718005808873469</v>
+        <v>6.300797296474734</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06864316320620277</v>
+        <v>0.2021058814317575</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6768969453516311</v>
+        <v>-0.09044575429604776</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8289790755272731</v>
+        <v>-0.6003280481263688</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8559895678888526</v>
+        <v>-0.4340661837219869</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.0112766404465052</v>
+        <v>-0.02241974526561569</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.4287689258829079</v>
+        <v>-0.6025886018617124</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.04271103439447119</v>
+        <v>-0.07924093257031306</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>78.02844382352893</v>
+        <v>75.50911168633812</v>
       </c>
       <c r="B48" t="n">
-        <v>105.5556645207423</v>
+        <v>165.3619000856194</v>
       </c>
       <c r="C48" t="n">
-        <v>47.48355083751505</v>
+        <v>45.8718014771756</v>
       </c>
       <c r="D48" t="n">
-        <v>10.63643365364072</v>
+        <v>11.39306199099877</v>
       </c>
       <c r="E48" t="n">
-        <v>3.410146412659475</v>
+        <v>3.952092642472704</v>
       </c>
       <c r="F48" t="n">
-        <v>9.351100344594126</v>
+        <v>9.068861071914089</v>
       </c>
       <c r="G48" t="n">
-        <v>0.05699178320094503</v>
+        <v>0.0630559172128156</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.7216505213203492</v>
+        <v>-0.6497090494120059</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8499193352922166</v>
+        <v>-0.8164764458950412</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.8818258821803806</v>
+        <v>-0.839877963305574</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.06590056973800275</v>
+        <v>-0.03748302241629996</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.4578779162804953</v>
+        <v>-0.413002420765159</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.03178521438932176</v>
+        <v>-0.0826225504834667</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>52.37087747582229</v>
+        <v>74.32396531613372</v>
       </c>
       <c r="B49" t="n">
-        <v>96.18067137466642</v>
+        <v>174.835011530414</v>
       </c>
       <c r="C49" t="n">
-        <v>47.84609805777509</v>
+        <v>45.51325319777266</v>
       </c>
       <c r="D49" t="n">
-        <v>7.786760731360153</v>
+        <v>11.61840843855696</v>
       </c>
       <c r="E49" t="n">
-        <v>3.334785078636669</v>
+        <v>3.724965293585869</v>
       </c>
       <c r="F49" t="n">
-        <v>5.911196617622525</v>
+        <v>8.887432273866558</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2353759386363881</v>
+        <v>0.06681135578941659</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1158618636109061</v>
+        <v>-0.6331075464598019</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6088524653340838</v>
+        <v>-0.8090216279447913</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.4537480057183384</v>
+        <v>-0.8297273804305959</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03433338661429561</v>
+        <v>-0.04536834808172663</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.5977458725000493</v>
+        <v>-0.4045582528774527</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02037595771260863</v>
+        <v>-0.002945155060589816</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>58.20776884691364</v>
+        <v>78.36049102549076</v>
       </c>
       <c r="B50" t="n">
-        <v>87.9069258225237</v>
+        <v>77.27310745166992</v>
       </c>
       <c r="C50" t="n">
-        <v>46.20417085374159</v>
+        <v>45.53149042211687</v>
       </c>
       <c r="D50" t="n">
-        <v>6.912115595906851</v>
+        <v>10.57256143895776</v>
       </c>
       <c r="E50" t="n">
-        <v>2.847492040803674</v>
+        <v>4.898916894900816</v>
       </c>
       <c r="F50" t="n">
-        <v>6.727910263851522</v>
+        <v>9.400179080388806</v>
       </c>
       <c r="G50" t="n">
-        <v>0.157761875030151</v>
+        <v>0.05494518097489804</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.3529147835625415</v>
+        <v>-0.6887113600803335</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6957710744234481</v>
+        <v>-0.8352593485493212</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.6392498816734095</v>
+        <v>-0.8634217442638132</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.008800645466446825</v>
+        <v>-0.02905297110534129</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.6365031929872845</v>
+        <v>-0.4627036826911808</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.04398707215522008</v>
+        <v>-0.006997871581528592</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50.24670462801242</v>
+        <v>69.28442689647763</v>
       </c>
       <c r="B51" t="n">
-        <v>94.78434726260872</v>
+        <v>154.3807046690737</v>
       </c>
       <c r="C51" t="n">
-        <v>47.49348221003836</v>
+        <v>45.53217068613971</v>
       </c>
       <c r="D51" t="n">
-        <v>7.983506638520311</v>
+        <v>12.68108873897812</v>
       </c>
       <c r="E51" t="n">
-        <v>3.329858334301797</v>
+        <v>3.513350642037601</v>
       </c>
       <c r="F51" t="n">
-        <v>5.60593095229062</v>
+        <v>8.253546417619928</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2755231832484016</v>
+        <v>0.08681536465511271</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0006573137736204951</v>
+        <v>-0.5488280428336704</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5689996240436421</v>
+        <v>-0.77229257093834</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.3571389277237538</v>
+        <v>-0.775880510996502</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.0008556320374273461</v>
+        <v>-0.12086410573251</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5836412331297509</v>
+        <v>-0.3686515416374031</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.03138821409704069</v>
+        <v>-0.00714904136437905</v>
       </c>
     </row>
   </sheetData>
